--- a/output/graficos_regionales/plot_regional_serie_i_ingr_s_2022_maule.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_s_2022_maule.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:37</t>
+    <t xml:space="preserve">2026-10-05 01:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -513,7 +513,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>642146.62</v>
+        <v>642146.63</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>837930.75</v>
@@ -590,7 +590,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>867479.12</v>
+        <v>867479.13</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>1104330.75</v>
@@ -604,7 +604,7 @@
         <v>925028.19</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1163774.62</v>
+        <v>1163774.63</v>
       </c>
     </row>
     <row r="13">
